--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
   <si>
     <t>Package</t>
   </si>
@@ -233,22 +233,31 @@
     <t>1.0.0</t>
   </si>
   <si>
+    <t>MyPojoRequest</t>
+  </si>
+  <si>
+    <t>com.anaptecs.jeaf.junit.validationgroups</t>
+  </si>
+  <si>
+    <t>propertyWithNewConstraints</t>
+  </si>
+  <si>
     <t>MyPOJOResponse</t>
   </si>
   <si>
-    <t>com.anaptecs.jeaf.junit.validationgroups</t>
-  </si>
-  <si>
     <t>formerMandatoryProperty</t>
   </si>
   <si>
-    <t>MyPojoRequest</t>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
   </si>
   <si>
     <t>upcomingMandatoryProperty</t>
   </si>
   <si>
-    <t>propertyWithNewConstraints</t>
+    <t>Property will become mandatory in the future</t>
   </si>
 </sst>
 </file>
@@ -1147,33 +1156,33 @@
         <v>11</v>
       </c>
       <c r="F17" t="s" s="11">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s" s="11">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="9">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s" s="9">
         <v>65</v>
       </c>
       <c r="C18" t="s" s="9">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s" s="9">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s" s="11">
         <v>69</v>
       </c>
-      <c r="D18" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s" s="10">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s" s="11">
-        <v>11</v>
-      </c>
       <c r="G18" t="s" s="11">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
   <si>
     <t>Package</t>
   </si>
@@ -258,6 +258,21 @@
   </si>
   <si>
     <t>Property will become mandatory in the future</t>
+  </si>
+  <si>
+    <t>OtherPojo</t>
+  </si>
+  <si>
+    <t>v6Property</t>
+  </si>
+  <si>
+    <t>Property will become mandatory.</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
   </si>
 </sst>
 </file>
@@ -760,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="9" width="31.5"/>
@@ -1185,6 +1200,29 @@
         <v>70</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="s" s="9">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s" s="9">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s" s="9">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s" s="9">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s" s="11">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s" s="11">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
   <si>
     <t>Package</t>
   </si>
@@ -233,22 +233,46 @@
     <t>1.0.0</t>
   </si>
   <si>
+    <t>MyPojoRequest</t>
+  </si>
+  <si>
+    <t>com.anaptecs.jeaf.junit.validationgroups</t>
+  </si>
+  <si>
+    <t>propertyWithNewConstraints</t>
+  </si>
+  <si>
     <t>MyPOJOResponse</t>
   </si>
   <si>
-    <t>com.anaptecs.jeaf.junit.validationgroups</t>
-  </si>
-  <si>
     <t>formerMandatoryProperty</t>
   </si>
   <si>
-    <t>MyPojoRequest</t>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
   </si>
   <si>
     <t>upcomingMandatoryProperty</t>
   </si>
   <si>
-    <t>propertyWithNewConstraints</t>
+    <t>Property will become mandatory in the future</t>
+  </si>
+  <si>
+    <t>OtherPojo</t>
+  </si>
+  <si>
+    <t>v6Property</t>
+  </si>
+  <si>
+    <t>Property will become mandatory.</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
   </si>
 </sst>
 </file>
@@ -751,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="9" width="31.5"/>
@@ -1147,33 +1171,56 @@
         <v>11</v>
       </c>
       <c r="F17" t="s" s="11">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s" s="11">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="9">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s" s="9">
         <v>65</v>
       </c>
       <c r="C18" t="s" s="9">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s" s="9">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s" s="11">
         <v>69</v>
       </c>
-      <c r="D18" t="s" s="9">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s" s="10">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s" s="11">
-        <v>11</v>
-      </c>
       <c r="G18" t="s" s="11">
-        <v>11</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="9">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s" s="9">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s" s="9">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s" s="9">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s" s="10">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s" s="11">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s" s="11">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
